--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsRecon.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsRecon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20535" windowHeight="4125"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
     <t>{.supplierName}</t>
   </si>
   <si>
-    <t>{.fileName}</t>
+    <t>{.sheetName}</t>
   </si>
   <si>
     <t>{.checkStatusName}</t>
@@ -89,7 +89,7 @@
     <t>{.matchStatusName}</t>
   </si>
   <si>
-    <t>{.confirmStatusName}</t>
+    <t>{.reconciliationStatusName}</t>
   </si>
   <si>
     <t>{.importCount}</t>
@@ -1055,10 +1055,10 @@
   <cols>
     <col min="1" max="1" width="13.25" customWidth="1"/>
     <col min="2" max="2" width="17.5" customWidth="1"/>
-    <col min="3" max="3" width="14.125" customWidth="1"/>
+    <col min="3" max="3" width="18.625" customWidth="1"/>
     <col min="4" max="4" width="13.125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16.875" customWidth="1"/>
+    <col min="6" max="6" width="23.75" customWidth="1"/>
     <col min="7" max="7" width="13.25" customWidth="1"/>
     <col min="9" max="9" width="15.125" customWidth="1"/>
     <col min="10" max="10" width="16.25" customWidth="1"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsRecon.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsRecon.xlsx
@@ -80,7 +80,7 @@
     <t>{.supplierName}</t>
   </si>
   <si>
-    <t>{.sheetName}</t>
+    <t>{.fileName}</t>
   </si>
   <si>
     <t>{.checkStatusName}</t>
